--- a/test-results/automation-reports/test-cases.xlsx
+++ b/test-results/automation-reports/test-cases.xlsx
@@ -27,7 +27,7 @@
     <t>Execution Identifier</t>
   </si>
   <si>
-    <t>2026-09-15_23-18-31</t>
+    <t>2026-09-16_18-35-25</t>
   </si>
   <si>
     <t>Historical Mode</t>
@@ -39,25 +39,25 @@
     <t>Execution Start Time</t>
   </si>
   <si>
-    <t>2026-09-15T17:48:31.356Z</t>
+    <t>2026-09-16T13:05:25.420Z</t>
   </si>
   <si>
     <t>Execution End Time</t>
   </si>
   <si>
-    <t>2026-09-15T17:52:59.118Z</t>
+    <t>2026-09-16T13:08:32.857Z</t>
   </si>
   <si>
     <t>Total Execution Duration</t>
   </si>
   <si>
-    <t>4m 28s</t>
+    <t>3m 7s</t>
   </si>
   <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>2026-09-15T17:52:59.133Z</t>
+    <t>2026-09-16T13:08:32.869Z</t>
   </si>
   <si>
     <t>Documented Test Cases</t>
@@ -1041,7 +1041,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1049,7 +1049,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
@@ -1063,7 +1063,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
@@ -2017,10 +2017,10 @@
         <v>159</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -2040,10 +2040,10 @@
         <v>160</v>
       </c>
       <c r="B3" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -2063,10 +2063,10 @@
         <v>161</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>

--- a/test-results/automation-reports/test-cases.xlsx
+++ b/test-results/automation-reports/test-cases.xlsx
@@ -27,7 +27,7 @@
     <t>Execution Identifier</t>
   </si>
   <si>
-    <t>2026-09-16_18-35-25</t>
+    <t>2026-09-17_17-19-37</t>
   </si>
   <si>
     <t>Historical Mode</t>
@@ -39,25 +39,25 @@
     <t>Execution Start Time</t>
   </si>
   <si>
-    <t>2026-09-16T13:05:25.420Z</t>
+    <t>2026-09-17T11:49:37.263Z</t>
   </si>
   <si>
     <t>Execution End Time</t>
   </si>
   <si>
-    <t>2026-09-16T13:08:32.857Z</t>
+    <t>2026-09-17T11:51:44.550Z</t>
   </si>
   <si>
     <t>Total Execution Duration</t>
   </si>
   <si>
-    <t>3m 7s</t>
+    <t>2m 7s</t>
   </si>
   <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>2026-09-16T13:08:32.869Z</t>
+    <t>2026-09-17T11:51:44.556Z</t>
   </si>
   <si>
     <t>Documented Test Cases</t>

--- a/test-results/automation-reports/test-cases.xlsx
+++ b/test-results/automation-reports/test-cases.xlsx
@@ -27,7 +27,7 @@
     <t>Execution Identifier</t>
   </si>
   <si>
-    <t>2026-09-17_17-19-37</t>
+    <t>2026-09-18_05-48-22</t>
   </si>
   <si>
     <t>Historical Mode</t>
@@ -39,25 +39,25 @@
     <t>Execution Start Time</t>
   </si>
   <si>
-    <t>2026-09-17T11:49:37.263Z</t>
+    <t>2026-09-18T00:18:22.724Z</t>
   </si>
   <si>
     <t>Execution End Time</t>
   </si>
   <si>
-    <t>2026-09-17T11:51:44.550Z</t>
+    <t>2026-09-18T00:22:32.485Z</t>
   </si>
   <si>
     <t>Total Execution Duration</t>
   </si>
   <si>
-    <t>2m 7s</t>
+    <t>4m 10s</t>
   </si>
   <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>2026-09-17T11:51:44.556Z</t>
+    <t>2026-09-18T00:22:32.499Z</t>
   </si>
   <si>
     <t>Documented Test Cases</t>
